--- a/Ablation_Study/data/lstm_modality_outputs/lstm_modality_summary.xlsx
+++ b/Ablation_Study/data/lstm_modality_outputs/lstm_modality_summary.xlsx
@@ -528,46 +528,46 @@
         <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>1.785354733467102</v>
+        <v>1.43099582195282</v>
       </c>
       <c r="E2" t="n">
-        <v>2.388585336260745</v>
+        <v>2.030331565388121</v>
       </c>
       <c r="F2" t="n">
-        <v>3.375311136245728</v>
+        <v>3.130031585693359</v>
       </c>
       <c r="G2" t="n">
-        <v>4.043708416638007</v>
+        <v>3.847620930001276</v>
       </c>
       <c r="H2" t="n">
-        <v>1.927646994590759</v>
+        <v>1.259002208709717</v>
       </c>
       <c r="I2" t="n">
-        <v>2.288663966146836</v>
+        <v>1.561837093874821</v>
       </c>
       <c r="J2" t="n">
-        <v>2.102865695953369</v>
+        <v>1.480043292045593</v>
       </c>
       <c r="K2" t="n">
-        <v>2.462293850552717</v>
+        <v>1.767151366926031</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496711730957031</v>
+        <v>1.311671376228333</v>
       </c>
       <c r="M2" t="n">
-        <v>1.998649379542643</v>
+        <v>1.627502128962986</v>
       </c>
       <c r="N2" t="n">
-        <v>1.107744812965393</v>
+        <v>0.8067384362220764</v>
       </c>
       <c r="O2" t="n">
-        <v>1.328952710899798</v>
+        <v>1.052061527643121</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7018468379974365</v>
+        <v>0.5984877347946167</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.904914859012417</v>
+        <v>0.7820050977360261</v>
       </c>
     </row>
     <row r="3">
@@ -583,46 +583,46 @@
         <v>51</v>
       </c>
       <c r="D3" t="n">
-        <v>3.159435510635376</v>
+        <v>3.247110605239868</v>
       </c>
       <c r="E3" t="n">
-        <v>4.241314483790967</v>
+        <v>4.254459509763237</v>
       </c>
       <c r="F3" t="n">
-        <v>5.343535900115967</v>
+        <v>5.167551040649414</v>
       </c>
       <c r="G3" t="n">
-        <v>6.597953721923972</v>
+        <v>6.367267481763757</v>
       </c>
       <c r="H3" t="n">
-        <v>4.61579418182373</v>
+        <v>5.190637111663818</v>
       </c>
       <c r="I3" t="n">
-        <v>5.209038017920733</v>
+        <v>5.725745419944348</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8684401512146</v>
+        <v>2.88797664642334</v>
       </c>
       <c r="K3" t="n">
-        <v>3.857447216095559</v>
+        <v>3.684685489685374</v>
       </c>
       <c r="L3" t="n">
-        <v>2.537869215011597</v>
+        <v>2.615913152694702</v>
       </c>
       <c r="M3" t="n">
-        <v>3.108320968098799</v>
+        <v>3.348238490425903</v>
       </c>
       <c r="N3" t="n">
-        <v>2.181983709335327</v>
+        <v>2.125144720077515</v>
       </c>
       <c r="O3" t="n">
-        <v>2.913129314492253</v>
+        <v>2.582540718636499</v>
       </c>
       <c r="P3" t="n">
-        <v>1.408990025520325</v>
+        <v>1.495441675186157</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.058527154587254</v>
+        <v>1.954266817119845</v>
       </c>
     </row>
     <row r="4">
@@ -638,46 +638,46 @@
         <v>51</v>
       </c>
       <c r="D4" t="n">
-        <v>2.613449335098267</v>
+        <v>2.326907396316528</v>
       </c>
       <c r="E4" t="n">
-        <v>3.481206847767504</v>
+        <v>3.106821363005671</v>
       </c>
       <c r="F4" t="n">
-        <v>4.964630603790283</v>
+        <v>4.15489387512207</v>
       </c>
       <c r="G4" t="n">
-        <v>6.157632585368868</v>
+        <v>5.299801718403674</v>
       </c>
       <c r="H4" t="n">
-        <v>3.533115863800049</v>
+        <v>2.932734727859497</v>
       </c>
       <c r="I4" t="n">
-        <v>3.952248819224941</v>
+        <v>3.356527567774831</v>
       </c>
       <c r="J4" t="n">
-        <v>2.264342069625854</v>
+        <v>2.23751425743103</v>
       </c>
       <c r="K4" t="n">
-        <v>2.670134217107021</v>
+        <v>2.627693157119456</v>
       </c>
       <c r="L4" t="n">
-        <v>1.949369788169861</v>
+        <v>1.993972063064575</v>
       </c>
       <c r="M4" t="n">
-        <v>2.28853405786383</v>
+        <v>2.478410001627946</v>
       </c>
       <c r="N4" t="n">
-        <v>1.723714232444763</v>
+        <v>1.585327625274658</v>
       </c>
       <c r="O4" t="n">
-        <v>2.001152779232835</v>
+        <v>1.81390333109869</v>
       </c>
       <c r="P4" t="n">
-        <v>1.245521545410156</v>
+        <v>1.057002544403076</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.674657484875755</v>
+        <v>1.490751444254049</v>
       </c>
     </row>
   </sheetData>
